--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/750000/Output_0_9.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/750000/Output_0_9.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>320071.4256334111</v>
+        <v>298487.0049003611</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547406</v>
+        <v>3013503.893776015</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745723</v>
+        <v>20373567.14494819</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4812396.678818937</v>
+        <v>4789054.529283858</v>
       </c>
     </row>
     <row r="11">
@@ -1174,19 +1174,19 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1217,13 +1217,13 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1247,10 +1247,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>22.15420867374214</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1320,19 +1320,19 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>19.82224313344376</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1405,16 +1405,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1448,19 +1448,19 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>22.15420867374215</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1557,19 +1557,19 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>19.82224313344376</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1606,16 +1606,16 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,19 +1685,19 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>22.15420867374215</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1767,19 +1767,19 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2741920426674241</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1846,16 +1846,16 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2.361305680129117</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1879,16 +1879,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>14.67170078545518</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1961,19 +1961,19 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>24.66239999999999</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="W18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -2034,19 +2034,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T19" t="n">
-        <v>22.02246762618611</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2068,22 +2068,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>230.2038249569697</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2147,31 +2147,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>145.3912560091964</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>137.3435171632106</v>
+        <v>106.5083957652447</v>
       </c>
       <c r="H21" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2308,19 +2308,19 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2362,16 +2362,16 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="W23" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2387,19 +2387,19 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>157.5478344350873</v>
+        <v>79.78832327157356</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2438,13 +2438,13 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>21.18375537072436</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2587,10 +2587,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>209.0200695862453</v>
@@ -2599,10 +2599,10 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>102.2970636939287</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="27">
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
         <v>137.3435171632106</v>
@@ -2642,7 +2642,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>79.78832327157352</v>
       </c>
       <c r="J27" t="n">
         <v>0.7465913262578567</v>
@@ -2669,19 +2669,19 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>86.85840332732083</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2757,10 +2757,10 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>130.4655268502615</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -2788,13 +2788,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>230.2038249569697</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2836,7 +2836,7 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>220.1862512213238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>149.2581321583394</v>
+        <v>185.12254643689</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X30" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -2988,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -3025,10 +3025,10 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3064,25 +3064,25 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>70.34400780127524</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>167.4320114308427</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -3098,22 +3098,22 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>6.898601502952458</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
-        <v>18.29453910334675</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3143,16 +3143,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -3183,67 +3183,67 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3253,16 +3253,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>29.51218284430544</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -3298,10 +3298,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3310,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -3319,10 +3319,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>215</v>
+        <v>212.2853856434421</v>
       </c>
     </row>
     <row r="36">
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>76.09118681301986</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3353,10 +3353,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3383,25 +3383,25 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>197.8524234702646</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="37">
@@ -3477,10 +3477,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="Y37" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3490,16 +3490,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>35.49211325806009</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3535,13 +3535,13 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -3550,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="39">
@@ -3578,19 +3578,19 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>157.6450804554009</v>
+        <v>70.73885857389313</v>
       </c>
       <c r="F39" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>22.46629018934509</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3620,16 +3620,16 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -3693,19 +3693,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>47.02492433367362</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -3727,16 +3727,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>187.9840913941556</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3784,19 +3784,19 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="X41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>177.6197007854552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -3815,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>24.04248813035636</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3857,22 +3857,22 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="V42" t="n">
-        <v>35.62153536935082</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="X42" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>205.6826957773044</v>
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>29.09675891541198</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.834132652785714</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>100.8903465994381</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>48.36509407418561</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>81.62201144066449</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>29.09675891541198</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2.834132652785714</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>100.8903465994381</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>48.36509407418561</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>81.62201144066449</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>29.09675891541198</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2.834132652785714</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>103.72303834074</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>77.46041207811371</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>28.18072336510073</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>53.92072336510073</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>79.66072336510072</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.24</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="C17" t="n">
-        <v>2.24</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="D17" t="n">
-        <v>2.24</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="E17" t="n">
-        <v>2.24</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="F17" t="n">
-        <v>2.24</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>70.01461603622408</v>
       </c>
       <c r="H17" t="n">
-        <v>2.24</v>
+        <v>42.14590365206637</v>
       </c>
       <c r="I17" t="n">
-        <v>2.24</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>28.84</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L17" t="n">
-        <v>28.84</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="M17" t="n">
-        <v>56.56</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="N17" t="n">
-        <v>84.28</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="O17" t="n">
-        <v>112</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>101.9083846317729</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="R17" t="n">
-        <v>87.08848484848485</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="S17" t="n">
-        <v>58.80565656565657</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="T17" t="n">
-        <v>30.52282828282829</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="U17" t="n">
-        <v>2.24</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="V17" t="n">
-        <v>2.24</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="W17" t="n">
-        <v>2.24</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="X17" t="n">
-        <v>2.24</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.24</v>
+        <v>72.39977328887976</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30.52282828282829</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C18" t="n">
-        <v>30.52282828282829</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D18" t="n">
-        <v>30.52282828282829</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E18" t="n">
-        <v>30.52282828282829</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F18" t="n">
-        <v>30.52282828282829</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G18" t="n">
-        <v>30.52282828282829</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>28.84</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L18" t="n">
-        <v>28.84</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="M18" t="n">
-        <v>56.56</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N18" t="n">
-        <v>84.28</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="O18" t="n">
-        <v>84.28</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P18" t="n">
-        <v>84.28</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S18" t="n">
-        <v>87.08848484848485</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="T18" t="n">
-        <v>87.08848484848485</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="U18" t="n">
-        <v>87.08848484848485</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="V18" t="n">
-        <v>87.08848484848485</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W18" t="n">
-        <v>58.80565656565657</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X18" t="n">
-        <v>58.80565656565657</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y18" t="n">
-        <v>58.80565656565657</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q19" t="n">
-        <v>81.05057335978395</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R19" t="n">
-        <v>52.76774507695567</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="S19" t="n">
-        <v>24.48491679412739</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="T19" t="n">
-        <v>2.24</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="U19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>720.5656565656566</v>
+        <v>495.259035872464</v>
       </c>
       <c r="C20" t="n">
-        <v>477.1313131313132</v>
+        <v>495.259035872464</v>
       </c>
       <c r="D20" t="n">
-        <v>262.7143434343434</v>
+        <v>495.259035872464</v>
       </c>
       <c r="E20" t="n">
-        <v>19.28</v>
+        <v>495.259035872464</v>
       </c>
       <c r="F20" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T20" t="n">
-        <v>964</v>
+        <v>738.7078125165641</v>
       </c>
       <c r="U20" t="n">
-        <v>964</v>
+        <v>738.7078125165641</v>
       </c>
       <c r="V20" t="n">
-        <v>964</v>
+        <v>738.7078125165641</v>
       </c>
       <c r="W20" t="n">
-        <v>964</v>
+        <v>495.259035872464</v>
       </c>
       <c r="X20" t="n">
-        <v>964</v>
+        <v>495.259035872464</v>
       </c>
       <c r="Y20" t="n">
-        <v>964</v>
+        <v>495.259035872464</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>964</v>
+        <v>286.10283626238</v>
       </c>
       <c r="C21" t="n">
-        <v>817.1401454452562</v>
+        <v>286.10283626238</v>
       </c>
       <c r="D21" t="n">
-        <v>668.2057357840049</v>
+        <v>286.10283626238</v>
       </c>
       <c r="E21" t="n">
-        <v>508.9682807785495</v>
+        <v>126.8653812569245</v>
       </c>
       <c r="F21" t="n">
-        <v>362.4337228054344</v>
+        <v>126.8653812569245</v>
       </c>
       <c r="G21" t="n">
-        <v>223.7028973880499</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H21" t="n">
-        <v>110.3337617956292</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I21" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M21" t="n">
-        <v>374.6006659261865</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N21" t="n">
-        <v>542.7665223866492</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="O21" t="n">
-        <v>781.3565223866492</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="P21" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S21" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T21" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="U21" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="V21" t="n">
-        <v>964</v>
+        <v>454.3181732824481</v>
       </c>
       <c r="W21" t="n">
-        <v>964</v>
+        <v>454.3181732824481</v>
       </c>
       <c r="X21" t="n">
-        <v>964</v>
+        <v>454.3181732824481</v>
       </c>
       <c r="Y21" t="n">
-        <v>964</v>
+        <v>454.3181732824481</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>749.5830303030303</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C23" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D23" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E23" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F23" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U23" t="n">
-        <v>964</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="V23" t="n">
-        <v>964</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="W23" t="n">
-        <v>749.5830303030303</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="X23" t="n">
-        <v>749.5830303030303</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y23" t="n">
-        <v>749.5830303030303</v>
+        <v>262.7299197543128</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>352.8722559832354</v>
+        <v>385.8949250843803</v>
       </c>
       <c r="C24" t="n">
-        <v>178.4192267021084</v>
+        <v>385.8949250843803</v>
       </c>
       <c r="D24" t="n">
-        <v>178.4192267021084</v>
+        <v>385.8949250843803</v>
       </c>
       <c r="E24" t="n">
-        <v>19.28</v>
+        <v>305.3006591534979</v>
       </c>
       <c r="F24" t="n">
-        <v>19.28</v>
+        <v>158.7661011803829</v>
       </c>
       <c r="G24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L24" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M24" t="n">
-        <v>542.7665223866492</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N24" t="n">
-        <v>542.7665223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="O24" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P24" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T24" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U24" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="V24" t="n">
-        <v>728.8478917682573</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="W24" t="n">
-        <v>728.8478917682573</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="X24" t="n">
-        <v>728.8478917682573</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="Y24" t="n">
-        <v>521.0875930033035</v>
+        <v>554.1102621044483</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>19.28</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="C26" t="n">
-        <v>19.28</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="D26" t="n">
-        <v>19.28</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="E26" t="n">
-        <v>19.28</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="F26" t="n">
-        <v>19.28</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S26" t="n">
-        <v>591.3940537960203</v>
+        <v>752.9257720901863</v>
       </c>
       <c r="T26" t="n">
-        <v>366.0447108019482</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="U26" t="n">
-        <v>122.6103673676048</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="V26" t="n">
-        <v>19.28</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="W26" t="n">
-        <v>19.28</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="X26" t="n">
-        <v>19.28</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="Y26" t="n">
-        <v>19.28</v>
+        <v>284.1276524520142</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>158.7649580701702</v>
+        <v>385.8949250843803</v>
       </c>
       <c r="C27" t="n">
-        <v>158.7649580701702</v>
+        <v>385.8949250843803</v>
       </c>
       <c r="D27" t="n">
-        <v>158.7649580701702</v>
+        <v>385.8949250843803</v>
       </c>
       <c r="E27" t="n">
-        <v>158.7649580701702</v>
+        <v>385.8949250843803</v>
       </c>
       <c r="F27" t="n">
-        <v>158.7649580701702</v>
+        <v>239.3603671112653</v>
       </c>
       <c r="G27" t="n">
-        <v>20.03413265278571</v>
+        <v>100.6295416938808</v>
       </c>
       <c r="H27" t="n">
-        <v>20.03413265278571</v>
+        <v>100.6295416938808</v>
       </c>
       <c r="I27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M27" t="n">
-        <v>613.1906659261865</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N27" t="n">
-        <v>851.7806659261865</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="O27" t="n">
-        <v>964</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>601.6773650668669</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U27" t="n">
-        <v>601.6773650668669</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="V27" t="n">
-        <v>366.5252568351241</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="W27" t="n">
-        <v>366.5252568351241</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="X27" t="n">
-        <v>366.5252568351241</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="Y27" t="n">
-        <v>158.7649580701702</v>
+        <v>554.1102621044483</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19.28</v>
+        <v>495.259035872464</v>
       </c>
       <c r="C29" t="n">
-        <v>19.28</v>
+        <v>495.259035872464</v>
       </c>
       <c r="D29" t="n">
-        <v>19.28</v>
+        <v>495.259035872464</v>
       </c>
       <c r="E29" t="n">
-        <v>19.28</v>
+        <v>251.810259228364</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>251.810259228364</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S29" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T29" t="n">
-        <v>728.5590416377008</v>
+        <v>738.7078125165641</v>
       </c>
       <c r="U29" t="n">
-        <v>485.1246982033574</v>
+        <v>495.259035872464</v>
       </c>
       <c r="V29" t="n">
-        <v>485.1246982033574</v>
+        <v>495.259035872464</v>
       </c>
       <c r="W29" t="n">
-        <v>485.1246982033574</v>
+        <v>495.259035872464</v>
       </c>
       <c r="X29" t="n">
-        <v>241.690354769014</v>
+        <v>495.259035872464</v>
       </c>
       <c r="Y29" t="n">
-        <v>19.28</v>
+        <v>495.259035872464</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>193.733029281127</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="C30" t="n">
-        <v>19.28</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="D30" t="n">
-        <v>19.28</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="E30" t="n">
-        <v>19.28</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="F30" t="n">
-        <v>19.28</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="G30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>144.6375600578374</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M30" t="n">
-        <v>234.7819638733197</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="N30" t="n">
-        <v>473.3719638733197</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="O30" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P30" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T30" t="n">
-        <v>964</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="U30" t="n">
-        <v>813.2342099410713</v>
+        <v>401.4607451716973</v>
       </c>
       <c r="V30" t="n">
-        <v>813.2342099410713</v>
+        <v>401.4607451716973</v>
       </c>
       <c r="W30" t="n">
-        <v>569.7998665067279</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="X30" t="n">
-        <v>361.9483663011951</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="Y30" t="n">
-        <v>361.9483663011951</v>
+        <v>158.0119685275972</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>463.6134235905177</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C32" t="n">
-        <v>463.6134235905177</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D32" t="n">
-        <v>463.6134235905177</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E32" t="n">
-        <v>246.4417064188005</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F32" t="n">
-        <v>29.26998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G32" t="n">
-        <v>29.26998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H32" t="n">
-        <v>29.26998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I32" t="n">
-        <v>29.26998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>120.2150059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>300.290857495581</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>504.9505276501126</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>710.8050498573519</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>860</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>849.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R32" t="n">
-        <v>849.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S32" t="n">
-        <v>849.9083846317729</v>
+        <v>731.528039392485</v>
       </c>
       <c r="T32" t="n">
-        <v>849.9083846317729</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="U32" t="n">
-        <v>849.9083846317729</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="V32" t="n">
-        <v>849.9083846317729</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="W32" t="n">
-        <v>849.9083846317729</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="X32" t="n">
-        <v>680.7851407622348</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y32" t="n">
-        <v>680.7851407622348</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>435.0679840633289</v>
+        <v>481.7099827492369</v>
       </c>
       <c r="C33" t="n">
-        <v>435.0679840633289</v>
+        <v>474.7416984028202</v>
       </c>
       <c r="D33" t="n">
-        <v>435.0679840633289</v>
+        <v>325.807288741569</v>
       </c>
       <c r="E33" t="n">
-        <v>416.5886516357059</v>
+        <v>166.5698337361135</v>
       </c>
       <c r="F33" t="n">
-        <v>270.0540936625908</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G33" t="n">
-        <v>131.3232682452064</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H33" t="n">
-        <v>17.95413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I33" t="n">
-        <v>17.95413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>142.5575600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L33" t="n">
-        <v>355.4075600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M33" t="n">
-        <v>568.2575600578374</v>
+        <v>383.2428491569326</v>
       </c>
       <c r="N33" t="n">
-        <v>781.1075600578374</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O33" t="n">
-        <v>790.6054414866707</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P33" t="n">
-        <v>790.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>860</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S33" t="n">
-        <v>860</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T33" t="n">
-        <v>860</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="U33" t="n">
-        <v>642.8282828282828</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="V33" t="n">
-        <v>642.8282828282828</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="W33" t="n">
-        <v>642.8282828282828</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="X33" t="n">
-        <v>642.8282828282828</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="Y33" t="n">
-        <v>435.0679840633289</v>
+        <v>481.7099827492369</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C34" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D34" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L34" t="n">
-        <v>44.51412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M34" t="n">
-        <v>83.70216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N34" t="n">
-        <v>127.3930138553715</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y34" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>47.01028570131862</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C35" t="n">
-        <v>47.01028570131862</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D35" t="n">
-        <v>47.01028570131862</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>120.2150059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>300.290857495581</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>513.1408574955809</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>621.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>849.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R35" t="n">
-        <v>698.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S35" t="n">
-        <v>698.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T35" t="n">
-        <v>698.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U35" t="n">
-        <v>698.5254372164702</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="V35" t="n">
-        <v>698.5254372164702</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="W35" t="n">
-        <v>698.5254372164702</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X35" t="n">
-        <v>481.353720044753</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y35" t="n">
-        <v>264.1820028730358</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.95413265278571</v>
+        <v>186.4405569126723</v>
       </c>
       <c r="C36" t="n">
-        <v>17.95413265278571</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="D36" t="n">
-        <v>17.95413265278571</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="E36" t="n">
-        <v>17.95413265278571</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="F36" t="n">
-        <v>17.95413265278571</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="G36" t="n">
-        <v>17.95413265278571</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="H36" t="n">
-        <v>17.95413265278571</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="I36" t="n">
-        <v>17.95413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>142.5575600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L36" t="n">
-        <v>355.4075600578374</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M36" t="n">
-        <v>568.2575600578374</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="N36" t="n">
-        <v>781.1075600578374</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="O36" t="n">
-        <v>781.1075600578374</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P36" t="n">
-        <v>790.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S36" t="n">
-        <v>860</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T36" t="n">
-        <v>860</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="U36" t="n">
-        <v>860</v>
+        <v>562.4161926976942</v>
       </c>
       <c r="V36" t="n">
-        <v>642.8282828282828</v>
+        <v>562.4161926976942</v>
       </c>
       <c r="W36" t="n">
-        <v>425.6565656565656</v>
+        <v>562.4161926976942</v>
       </c>
       <c r="X36" t="n">
-        <v>217.8050654510328</v>
+        <v>562.4161926976942</v>
       </c>
       <c r="Y36" t="n">
-        <v>17.95413265278571</v>
+        <v>354.6558939327403</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L37" t="n">
-        <v>44.51412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M37" t="n">
-        <v>83.70216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N37" t="n">
-        <v>127.3930138553715</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O37" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P37" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q37" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R37" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S37" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T37" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U37" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V37" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W37" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X37" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>53.05061945258595</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="C38" t="n">
-        <v>53.05061945258595</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="D38" t="n">
-        <v>53.05061945258595</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E38" t="n">
-        <v>53.05061945258595</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F38" t="n">
-        <v>53.05061945258595</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G38" t="n">
-        <v>53.05061945258595</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H38" t="n">
-        <v>53.05061945258595</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I38" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>22.36462077340309</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>202.4404723580617</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>415.2904723580617</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>621.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q38" t="n">
-        <v>849.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R38" t="n">
-        <v>698.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S38" t="n">
-        <v>487.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T38" t="n">
-        <v>487.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U38" t="n">
-        <v>487.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V38" t="n">
-        <v>487.3940537960203</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="W38" t="n">
-        <v>487.3940537960203</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X38" t="n">
-        <v>487.3940537960203</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y38" t="n">
-        <v>270.2223366243031</v>
+        <v>477.1596022224361</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>484.3960608094349</v>
+        <v>90.73453560909468</v>
       </c>
       <c r="C39" t="n">
-        <v>484.3960608094349</v>
+        <v>90.73453560909468</v>
       </c>
       <c r="D39" t="n">
-        <v>484.3960608094349</v>
+        <v>90.73453560909468</v>
       </c>
       <c r="E39" t="n">
-        <v>325.1586058039794</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F39" t="n">
-        <v>178.6240478308644</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G39" t="n">
-        <v>39.89322241347989</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H39" t="n">
-        <v>39.89322241347989</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>142.5575600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L39" t="n">
-        <v>355.4075600578374</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="M39" t="n">
-        <v>464.5065223866492</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="N39" t="n">
-        <v>464.5065223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O39" t="n">
-        <v>677.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P39" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R39" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S39" t="n">
-        <v>686.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T39" t="n">
-        <v>484.3960608094349</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U39" t="n">
-        <v>484.3960608094349</v>
+        <v>533.6469426057913</v>
       </c>
       <c r="V39" t="n">
-        <v>484.3960608094349</v>
+        <v>298.4948343740486</v>
       </c>
       <c r="W39" t="n">
-        <v>484.3960608094349</v>
+        <v>298.4948343740486</v>
       </c>
       <c r="X39" t="n">
-        <v>484.3960608094349</v>
+        <v>298.4948343740486</v>
       </c>
       <c r="Y39" t="n">
-        <v>484.3960608094349</v>
+        <v>90.73453560909468</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C40" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D40" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E40" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F40" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G40" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H40" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I40" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J40" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K40" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L40" t="n">
-        <v>44.51412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M40" t="n">
-        <v>83.70216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N40" t="n">
-        <v>127.3930138553715</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O40" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P40" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q40" t="n">
-        <v>151.7322904902707</v>
+        <v>877.0247885897328</v>
       </c>
       <c r="R40" t="n">
-        <v>151.7322904902707</v>
+        <v>877.0247885897328</v>
       </c>
       <c r="S40" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="T40" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="U40" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="V40" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="W40" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="X40" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y40" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>232.1915151515151</v>
+        <v>422.536925949487</v>
       </c>
       <c r="C41" t="n">
-        <v>232.1915151515151</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="D41" t="n">
-        <v>232.1915151515151</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="E41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>17.04</v>
+        <v>17.62165426160527</v>
       </c>
       <c r="L41" t="n">
-        <v>197.1158515846586</v>
+        <v>197.6975058462639</v>
       </c>
       <c r="M41" t="n">
-        <v>407.2904723580617</v>
+        <v>408.9875268274333</v>
       </c>
       <c r="N41" t="n">
-        <v>613.144994565301</v>
+        <v>614.8420490346726</v>
       </c>
       <c r="O41" t="n">
-        <v>762.339944707949</v>
+        <v>764.0369991773207</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U41" t="n">
-        <v>841.9083846317729</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="V41" t="n">
-        <v>841.9083846317729</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="W41" t="n">
-        <v>841.9083846317729</v>
+        <v>422.536925949487</v>
       </c>
       <c r="X41" t="n">
-        <v>626.7568694802578</v>
+        <v>422.536925949487</v>
       </c>
       <c r="Y41" t="n">
-        <v>447.3430303030303</v>
+        <v>422.536925949487</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.04</v>
+        <v>41.35928263520194</v>
       </c>
       <c r="C42" t="n">
-        <v>17.04</v>
+        <v>41.35928263520194</v>
       </c>
       <c r="D42" t="n">
-        <v>17.04</v>
+        <v>41.35928263520194</v>
       </c>
       <c r="E42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>142.3975600578374</v>
+        <v>142.4315011472248</v>
       </c>
       <c r="L42" t="n">
-        <v>353.2675600578374</v>
+        <v>142.4315011472248</v>
       </c>
       <c r="M42" t="n">
-        <v>564.1375600578374</v>
+        <v>353.7215221283943</v>
       </c>
       <c r="N42" t="n">
-        <v>775.0075600578374</v>
+        <v>459.7635558748512</v>
       </c>
       <c r="O42" t="n">
-        <v>852</v>
+        <v>671.0535768560208</v>
       </c>
       <c r="P42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S42" t="n">
-        <v>852</v>
+        <v>680.2797099200405</v>
       </c>
       <c r="T42" t="n">
-        <v>852</v>
+        <v>680.2797099200405</v>
       </c>
       <c r="U42" t="n">
-        <v>852</v>
+        <v>464.6996456600982</v>
       </c>
       <c r="V42" t="n">
-        <v>816.0186511420699</v>
+        <v>464.6996456600982</v>
       </c>
       <c r="W42" t="n">
-        <v>600.8671359905547</v>
+        <v>249.1195814001559</v>
       </c>
       <c r="X42" t="n">
-        <v>393.0156357850219</v>
+        <v>249.1195814001559</v>
       </c>
       <c r="Y42" t="n">
-        <v>185.255337020068</v>
+        <v>41.35928263520194</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="C43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L43" t="n">
-        <v>44.35412500771298</v>
+        <v>44.38806609710041</v>
       </c>
       <c r="M43" t="n">
-        <v>83.54216319993516</v>
+        <v>83.57610428932259</v>
       </c>
       <c r="N43" t="n">
-        <v>127.2330138553715</v>
+        <v>127.2669549447589</v>
       </c>
       <c r="O43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="P43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Q43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="R43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="S43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="T43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="U43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="V43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="W43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="X43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="Y43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
     </row>
     <row r="44">
@@ -8433,13 +8433,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L8" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M8" t="n">
-        <v>255.2957281767677</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N8" t="n">
         <v>229.4130635965909</v>
@@ -8448,7 +8448,7 @@
         <v>230.0982114216867</v>
       </c>
       <c r="P8" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8518,19 +8518,19 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>168.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
-        <v>156.2912070328283</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,16 +8594,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O10" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P10" t="n">
         <v>135.0065633140411</v>
@@ -8676,16 +8676,16 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M11" t="n">
-        <v>255.2957281767677</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N11" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P11" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8758,16 +8758,16 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>158.9239023638252</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,16 +8831,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O13" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P13" t="n">
         <v>135.0065633140411</v>
@@ -8907,16 +8907,16 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L14" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M14" t="n">
-        <v>256.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N14" t="n">
-        <v>254.3625585460859</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
         <v>230.0982114216867</v>
@@ -8992,16 +8992,16 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
-        <v>168.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N15" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>158.9239023638252</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
         <v>139.9817740860215</v>
@@ -9068,16 +9068,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O16" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P16" t="n">
         <v>135.0065633140411</v>
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>246.9585379136674</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L17" t="n">
-        <v>235.7664149699872</v>
+        <v>262.2416917349371</v>
       </c>
       <c r="M17" t="n">
-        <v>258.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N17" t="n">
-        <v>257.4130635965909</v>
+        <v>257.0030888569071</v>
       </c>
       <c r="O17" t="n">
-        <v>258.0982114216868</v>
+        <v>257.6882366820029</v>
       </c>
       <c r="P17" t="n">
-        <v>231.2329957552695</v>
+        <v>258.8230210155857</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9223,25 +9223,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>164.7101258430459</v>
+        <v>165.4314642346751</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797798742</v>
+        <v>166.1444050401903</v>
       </c>
       <c r="M18" t="n">
-        <v>170.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N18" t="n">
-        <v>159.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
-        <v>142.5962444444444</v>
+        <v>169.0715212093943</v>
       </c>
       <c r="P18" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
-        <v>167.9817740860215</v>
+        <v>167.5717993463377</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9384,7 +9384,7 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
-        <v>417.6046363682045</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M20" t="n">
         <v>449.5135334928325</v>
@@ -9466,19 +9466,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>301.2062135585481</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
-        <v>318.4627686399372</v>
+        <v>177.2597568922521</v>
       </c>
       <c r="Q21" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9703,19 +9703,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>311.9985353972331</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N24" t="n">
-        <v>131.3417120833333</v>
+        <v>231.1529892133072</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q24" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9940,16 +9940,16 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N27" t="n">
-        <v>372.3417120833333</v>
+        <v>301.2485028631349</v>
       </c>
       <c r="O27" t="n">
-        <v>255.9491071452661</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q27" t="n">
         <v>139.9817740860215</v>
@@ -10092,13 +10092,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L29" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M29" t="n">
-        <v>449.4569553105865</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N29" t="n">
         <v>437.3469244119842</v>
@@ -10174,22 +10174,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L30" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M30" t="n">
-        <v>233.1889872709904</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>312.5030352242461</v>
       </c>
       <c r="P30" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q30" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10335,7 +10335,7 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>437.0731727773048</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N32" t="n">
         <v>437.3469244119842</v>
@@ -10344,7 +10344,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P32" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10411,22 +10411,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L33" t="n">
-        <v>353.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
-        <v>357.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N33" t="n">
-        <v>346.3417120833333</v>
+        <v>292.5201795090609</v>
       </c>
       <c r="O33" t="n">
-        <v>152.1900640695285</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P33" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q33" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10569,13 +10569,13 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L35" t="n">
-        <v>417.6612145504504</v>
+        <v>417.6612145504505</v>
       </c>
       <c r="M35" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N35" t="n">
-        <v>338.5081515458031</v>
+        <v>437.3469244119842</v>
       </c>
       <c r="O35" t="n">
         <v>380.8001812627454</v>
@@ -10648,22 +10648,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L36" t="n">
-        <v>353.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M36" t="n">
-        <v>357.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N36" t="n">
-        <v>346.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O36" t="n">
-        <v>142.5962444444444</v>
+        <v>312.5030352242461</v>
       </c>
       <c r="P36" t="n">
-        <v>143.5682270394143</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q36" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10803,13 +10803,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>225.3066397049837</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
@@ -10885,16 +10885,16 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L39" t="n">
-        <v>353.5543797798742</v>
+        <v>299.7328472056018</v>
       </c>
       <c r="M39" t="n">
-        <v>252.3350059713232</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O39" t="n">
-        <v>357.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P39" t="n">
         <v>318.4627686399372</v>
@@ -11040,13 +11040,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>220.0898510449805</v>
+        <v>220.6430966734834</v>
       </c>
       <c r="L41" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>442.643829968084</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
         <v>437.3469244119842</v>
@@ -11122,19 +11122,19 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L42" t="n">
-        <v>351.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M42" t="n">
-        <v>355.1340339220183</v>
+        <v>355.5582975393612</v>
       </c>
       <c r="N42" t="n">
-        <v>344.3417120833333</v>
+        <v>238.4548774837949</v>
       </c>
       <c r="O42" t="n">
-        <v>220.3663858001642</v>
+        <v>356.0205080617874</v>
       </c>
       <c r="P42" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q42" t="n">
         <v>139.9817740860215</v>
@@ -23032,19 +23032,19 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T8" t="n">
-        <v>200.1950495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U8" t="n">
-        <v>225.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W8" t="n">
-        <v>323.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X8" t="n">
-        <v>343.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y8" t="n">
         <v>386.2379386560536</v>
@@ -23075,13 +23075,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I9" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -23105,10 +23105,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>74.15783415264313</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S9" t="n">
-        <v>149.5289624300957</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T9" t="n">
         <v>200.1647286948216</v>
@@ -23178,19 +23178,19 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S10" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T10" t="n">
-        <v>208.1233462948377</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U10" t="n">
         <v>286.3190293564909</v>
@@ -23263,16 +23263,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>126.9683179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S11" t="n">
-        <v>183.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T11" t="n">
-        <v>197.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U11" t="n">
-        <v>225.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23306,19 +23306,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
-        <v>122.9150037196417</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H12" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I12" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -23415,19 +23415,19 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R13" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S13" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T13" t="n">
-        <v>208.1233462948377</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U13" t="n">
         <v>286.3190293564909</v>
@@ -23464,16 +23464,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F14" t="n">
-        <v>383.9752457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>389.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H14" t="n">
-        <v>313.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I14" t="n">
-        <v>184.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -23543,19 +23543,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F15" t="n">
-        <v>122.9150037196417</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H15" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I15" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -23625,19 +23625,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.7167873157913</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H16" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I16" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J16" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23704,16 +23704,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>415.302737515135</v>
+        <v>412.9414318350059</v>
       </c>
       <c r="H17" t="n">
-        <v>339.4748021157671</v>
+        <v>311.884776855451</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>182.8858643100898</v>
       </c>
       <c r="J17" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>135.1974171556945</v>
+        <v>122.2790926808335</v>
       </c>
       <c r="S17" t="n">
-        <v>181.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T17" t="n">
-        <v>195.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U17" t="n">
-        <v>223.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23768,7 +23768,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>138.5331836498673</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C18" t="n">
         <v>172.7084989883157</v>
@@ -23786,7 +23786,7 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H18" t="n">
-        <v>84.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I18" t="n">
         <v>89.39663285141508</v>
@@ -23819,19 +23819,19 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S18" t="n">
-        <v>147.0207711038378</v>
+        <v>144.0931458435217</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>172.5747034345055</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9413820809748</v>
+        <v>198.3513568206587</v>
       </c>
       <c r="V18" t="n">
-        <v>232.8005871494253</v>
+        <v>208.4992929001388</v>
       </c>
       <c r="W18" t="n">
-        <v>223.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X18" t="n">
         <v>205.7729852034775</v>
@@ -23892,19 +23892,19 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q19" t="n">
-        <v>58.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>149.2933913771695</v>
+        <v>149.7033661168533</v>
       </c>
       <c r="S19" t="n">
-        <v>196.0165980369723</v>
+        <v>196.4265727766561</v>
       </c>
       <c r="T19" t="n">
-        <v>205.9231218020954</v>
+        <v>200.3555641679654</v>
       </c>
       <c r="U19" t="n">
-        <v>286.3190293564909</v>
+        <v>263.8702699959815</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23926,22 +23926,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C20" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D20" t="n">
-        <v>142.4102416206829</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E20" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F20" t="n">
-        <v>406.8760457417114</v>
+        <v>176.6722207847417</v>
       </c>
       <c r="G20" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H20" t="n">
         <v>339.4748021157671</v>
@@ -23980,7 +23980,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>251.3456529078365</v>
@@ -23989,7 +23989,7 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X20" t="n">
         <v>369.731100678469</v>
@@ -24005,31 +24005,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>27.31724297911936</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>30.83512139796595</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24053,10 +24053,10 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>200.1647286948216</v>
@@ -24065,7 +24065,7 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>251.6949831609196</v>
@@ -24099,7 +24099,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.9909793584588</v>
+        <v>34.80401177309074</v>
       </c>
       <c r="H22" t="n">
         <v>162.2271725074396</v>
@@ -24153,7 +24153,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y22" t="n">
-        <v>85.39768576672677</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="23">
@@ -24166,19 +24166,19 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C23" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D23" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F23" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H23" t="n">
         <v>339.4748021157671</v>
@@ -24220,16 +24220,16 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U23" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V23" t="n">
-        <v>327.7522584701349</v>
+        <v>115.4668728266928</v>
       </c>
       <c r="W23" t="n">
-        <v>136.9681687174131</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X23" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y23" t="n">
         <v>386.2379386560536</v>
@@ -24245,19 +24245,19 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09724602031360519</v>
+        <v>77.85675718382738</v>
       </c>
       <c r="F24" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>112.2354442364965</v>
@@ -24266,7 +24266,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24296,13 +24296,13 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
         <v>251.6949831609196</v>
@@ -24400,7 +24400,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C26" t="n">
         <v>365.2728917710076</v>
@@ -24415,7 +24415,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>415.302737515135</v>
+        <v>394.1189821444107</v>
       </c>
       <c r="H26" t="n">
         <v>339.4748021157671</v>
@@ -24445,10 +24445,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -24457,10 +24457,10 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V26" t="n">
-        <v>225.4551947762062</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W26" t="n">
         <v>349.240968717413</v>
@@ -24469,7 +24469,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="27">
@@ -24479,7 +24479,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>172.7084989883157</v>
@@ -24491,7 +24491,7 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F27" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -24500,7 +24500,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I27" t="n">
-        <v>89.39663285141508</v>
+        <v>9.60830957984156</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,19 +24527,19 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>113.3063253675008</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
         <v>251.6949831609196</v>
@@ -24600,7 +24600,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q28" t="n">
         <v>86.16204325169439</v>
@@ -24615,10 +24615,10 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U28" t="n">
-        <v>155.8535025062294</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V28" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W28" t="n">
         <v>286.522998336591</v>
@@ -24646,13 +24646,13 @@
         <v>354.683041620683</v>
       </c>
       <c r="E29" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F29" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>415.302737515135</v>
+        <v>185.0989125581653</v>
       </c>
       <c r="H29" t="n">
         <v>339.4748021157671</v>
@@ -24682,7 +24682,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
         <v>149.8691179411497</v>
@@ -24694,7 +24694,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>10.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24703,10 +24703,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X29" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>166.0516874347298</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="30">
@@ -24716,10 +24716,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
         <v>147.4450655646388</v>
@@ -24731,7 +24731,7 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>112.2354442364965</v>
@@ -24767,22 +24767,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>76.68324992263541</v>
+        <v>40.81883564408477</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
         <v>205.6826957773044</v>
@@ -24846,7 +24846,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S31" t="n">
-        <v>224.0165980369723</v>
+        <v>90.82963045160423</v>
       </c>
       <c r="T31" t="n">
         <v>227.9455894282815</v>
@@ -24864,7 +24864,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y31" t="n">
-        <v>85.39768576672677</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="32">
@@ -24874,7 +24874,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>167.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C32" t="n">
         <v>365.2728917710076</v>
@@ -24883,10 +24883,10 @@
         <v>354.683041620683</v>
       </c>
       <c r="E32" t="n">
-        <v>166.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F32" t="n">
-        <v>191.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
         <v>415.302737515135</v>
@@ -24898,7 +24898,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -24922,25 +24922,25 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>209.0200695862453</v>
+        <v>138.6760617849701</v>
       </c>
       <c r="T32" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W32" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X32" t="n">
-        <v>202.2990892476263</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y32" t="n">
         <v>386.2379386560536</v>
@@ -24956,22 +24956,22 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>172.7084989883157</v>
+        <v>165.8098974853633</v>
       </c>
       <c r="D33" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>139.3505413520542</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
         <v>89.39663285141508</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>10.94138208097482</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25041,7 +25041,7 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E34" t="n">
-        <v>13.24699506120112</v>
+        <v>146.4339626465692</v>
       </c>
       <c r="F34" t="n">
         <v>145.4210480229312</v>
@@ -25101,7 +25101,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y34" t="n">
-        <v>218.5846533520948</v>
+        <v>85.3976857667268</v>
       </c>
     </row>
     <row r="35">
@@ -25111,16 +25111,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>167.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C35" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D35" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E35" t="n">
-        <v>352.4181872279564</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F35" t="n">
         <v>406.8760457417114</v>
@@ -25156,10 +25156,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S35" t="n">
         <v>209.0200695862453</v>
@@ -25168,7 +25168,7 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U35" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25177,10 +25177,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X35" t="n">
-        <v>154.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y35" t="n">
-        <v>171.2379386560536</v>
+        <v>173.9525530126115</v>
       </c>
     </row>
     <row r="36">
@@ -25190,10 +25190,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>172.7084989883157</v>
+        <v>96.61731217529588</v>
       </c>
       <c r="D36" t="n">
         <v>147.4450655646388</v>
@@ -25211,10 +25211,10 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I36" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25241,25 +25241,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>17.80058714942527</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>36.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
-        <v>7.830272307039792</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -25335,10 +25335,10 @@
         <v>286.522998336591</v>
       </c>
       <c r="X37" t="n">
-        <v>225.7096553890372</v>
+        <v>92.52268780366916</v>
       </c>
       <c r="Y37" t="n">
-        <v>85.39768576672674</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="38">
@@ -25348,16 +25348,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>167.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C38" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D38" t="n">
-        <v>354.683041620683</v>
+        <v>142.3976559772408</v>
       </c>
       <c r="E38" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F38" t="n">
         <v>406.8760457417114</v>
@@ -25369,7 +25369,7 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I38" t="n">
-        <v>174.9837763123458</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J38" t="n">
         <v>11.94928935461252</v>
@@ -25393,13 +25393,13 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
         <v>223.0958495641314</v>
@@ -25408,7 +25408,7 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V38" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W38" t="n">
         <v>349.240968717413</v>
@@ -25417,7 +25417,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
-        <v>171.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="39">
@@ -25436,19 +25436,19 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>86.90622188150782</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
         <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
-        <v>66.93034266206999</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
         <v>0.7465913262578567</v>
@@ -25478,16 +25478,16 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
         <v>251.6949831609196</v>
@@ -25496,7 +25496,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -25551,19 +25551,19 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q40" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>177.2933913771695</v>
       </c>
       <c r="S40" t="n">
-        <v>224.0165980369723</v>
+        <v>176.9916737032986</v>
       </c>
       <c r="T40" t="n">
         <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>153.1320617711228</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25585,16 +25585,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>169.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C41" t="n">
-        <v>365.2728917710076</v>
+        <v>177.2888003768519</v>
       </c>
       <c r="D41" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E41" t="n">
-        <v>168.9303700722618</v>
+        <v>168.5061064549189</v>
       </c>
       <c r="F41" t="n">
         <v>406.8760457417114</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25642,19 +25642,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U41" t="n">
-        <v>251.3456529078365</v>
+        <v>37.92138929049358</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>349.240968717413</v>
+        <v>135.8167051000701</v>
       </c>
       <c r="X41" t="n">
-        <v>156.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y41" t="n">
-        <v>208.6182378705984</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="42">
@@ -25664,7 +25664,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
         <v>172.7084989883157</v>
@@ -25673,7 +25673,7 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
-        <v>157.6450804554009</v>
+        <v>133.6025923250446</v>
       </c>
       <c r="F42" t="n">
         <v>145.0692123933839</v>
@@ -25715,22 +25715,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9413820809748</v>
+        <v>12.5171184636319</v>
       </c>
       <c r="V42" t="n">
-        <v>197.1790517800744</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>38.69498316091961</v>
+        <v>38.27071954357669</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -25800,7 +25800,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U43" t="n">
-        <v>153.1320617711228</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350350.0795405005</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350350.0795405005</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350350.0795405007</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351994.6487060301</v>
+        <v>351669.2246312145</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>506779.7343245365</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205642</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205642</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488007.1404845365</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488007.1404845364</v>
+        <v>506790.0512205642</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488007.1404845364</v>
+        <v>506790.0512205642</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486563.0948045364</v>
+        <v>486869.422826439</v>
       </c>
     </row>
     <row r="16">
@@ -26267,43 +26267,43 @@
         <v>48378.33248915087</v>
       </c>
       <c r="D2" t="n">
-        <v>51690.99534204104</v>
+        <v>48378.33248915087</v>
       </c>
       <c r="E2" t="n">
-        <v>51690.99534204104</v>
+        <v>48378.33248915088</v>
       </c>
       <c r="F2" t="n">
-        <v>51690.99534204105</v>
+        <v>48378.33248915088</v>
       </c>
       <c r="G2" t="n">
-        <v>51933.63669433229</v>
+        <v>51885.62330624468</v>
       </c>
       <c r="H2" t="n">
-        <v>74770.78047411189</v>
+        <v>74772.30263909958</v>
       </c>
       <c r="I2" t="n">
-        <v>74770.78047411186</v>
+        <v>74772.30263909958</v>
       </c>
       <c r="J2" t="n">
-        <v>74770.78047411189</v>
+        <v>74772.30263909958</v>
       </c>
       <c r="K2" t="n">
-        <v>74770.78047411185</v>
+        <v>74772.30263909957</v>
       </c>
       <c r="L2" t="n">
-        <v>72001.05351411187</v>
+        <v>74772.30263909959</v>
       </c>
       <c r="M2" t="n">
-        <v>72001.05351411187</v>
+        <v>74772.30263909957</v>
       </c>
       <c r="N2" t="n">
-        <v>72001.05351411186</v>
+        <v>74772.30263909954</v>
       </c>
       <c r="O2" t="n">
-        <v>71787.99759411186</v>
+        <v>71833.1935317696</v>
       </c>
       <c r="P2" t="n">
-        <v>48378.33248915087</v>
+        <v>48378.33248915088</v>
       </c>
     </row>
     <row r="3">
@@ -26319,7 +26319,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>7562.01207347375</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>2099.754014286062</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2099.754014286062</v>
       </c>
       <c r="D4" t="n">
-        <v>22.532822180663</v>
+        <v>2099.754014286062</v>
       </c>
       <c r="E4" t="n">
-        <v>22.532822180663</v>
+        <v>2099.754014286062</v>
       </c>
       <c r="F4" t="n">
-        <v>22.532822180663</v>
+        <v>2099.754014286062</v>
       </c>
       <c r="G4" t="n">
-        <v>24.18327521124651</v>
+        <v>2278.927672807631</v>
       </c>
       <c r="H4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.11787725023</v>
       </c>
       <c r="I4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.11787725023</v>
       </c>
       <c r="J4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="K4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.11787725023</v>
       </c>
       <c r="L4" t="n">
-        <v>160.6823863208583</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="M4" t="n">
-        <v>160.6823863208583</v>
+        <v>3448.11787725023</v>
       </c>
       <c r="N4" t="n">
-        <v>160.6823863208583</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="O4" t="n">
-        <v>159.2331741996462</v>
+        <v>3297.970381927695</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2099.754014286062</v>
       </c>
     </row>
     <row r="5">
@@ -26423,40 +26423,40 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750.73248915088</v>
+        <v>12650.97847486482</v>
       </c>
       <c r="C6" t="n">
-        <v>14750.73248915087</v>
+        <v>12650.97847486482</v>
       </c>
       <c r="D6" t="n">
-        <v>8383.682519860376</v>
+        <v>12650.97847486482</v>
       </c>
       <c r="E6" t="n">
-        <v>50087.66251986037</v>
+        <v>46278.57847486482</v>
       </c>
       <c r="F6" t="n">
-        <v>50087.66251986038</v>
+        <v>46278.57847486482</v>
       </c>
       <c r="G6" t="n">
-        <v>49658.88341912105</v>
+        <v>40367.21002413608</v>
       </c>
       <c r="H6" t="n">
-        <v>2469.141330215272</v>
+        <v>-913.2711442440032</v>
       </c>
       <c r="I6" t="n">
-        <v>59938.45833021525</v>
+        <v>56670.51599808768</v>
       </c>
       <c r="J6" t="n">
-        <v>59938.45833021528</v>
+        <v>56670.51599808768</v>
       </c>
       <c r="K6" t="n">
-        <v>59938.45833021523</v>
+        <v>56670.51599808766</v>
       </c>
       <c r="L6" t="n">
-        <v>58768.37112779102</v>
+        <v>56670.51599808769</v>
       </c>
       <c r="M6" t="n">
-        <v>58768.37112779102</v>
+        <v>56670.51599808766</v>
       </c>
       <c r="N6" t="n">
-        <v>58768.371127791</v>
+        <v>56670.51599808763</v>
       </c>
       <c r="O6" t="n">
-        <v>58678.36441991221</v>
+        <v>55559.02792190747</v>
       </c>
       <c r="P6" t="n">
-        <v>48378.33248915087</v>
+        <v>46278.57847486482</v>
       </c>
     </row>
   </sheetData>
@@ -26733,40 +26733,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,13 +26892,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26907,34 +26907,34 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26950,43 +26950,43 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27191,7 +27191,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -35088,13 +35088,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -35103,7 +35103,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35173,19 +35173,19 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35249,16 +35249,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -35331,16 +35331,16 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35413,16 +35413,16 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35486,16 +35486,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -35562,16 +35562,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -35647,16 +35647,16 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -35723,16 +35723,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -35799,22 +35799,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>26.86868686868687</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="M17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35878,25 +35878,25 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>26.86868686868687</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36039,7 +36039,7 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
-        <v>181.8382213982173</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M20" t="n">
         <v>219.1673002655598</v>
@@ -36121,19 +36121,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>169.8645014752148</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
-        <v>184.4883612256069</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36358,19 +36358,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>99.8112771299739</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36595,16 +36595,16 @@
         <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N27" t="n">
-        <v>241</v>
+        <v>169.9067907798016</v>
       </c>
       <c r="O27" t="n">
-        <v>113.3528627008217</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36753,7 +36753,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M29" t="n">
-        <v>219.1107220833138</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N29" t="n">
         <v>207.9338608153932</v>
@@ -36829,22 +36829,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M30" t="n">
-        <v>91.05495334897203</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>169.9067907798016</v>
       </c>
       <c r="P30" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q30" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36990,7 +36990,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>206.726939550032</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N32" t="n">
         <v>207.9338608153932</v>
@@ -36999,7 +36999,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37066,22 +37066,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N33" t="n">
-        <v>215</v>
+        <v>161.1784674257276</v>
       </c>
       <c r="O33" t="n">
-        <v>9.59381962508408</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q33" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37227,10 +37227,10 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N35" t="n">
-        <v>109.0950879492122</v>
+        <v>207.9338608153932</v>
       </c>
       <c r="O35" t="n">
         <v>150.7019698410586</v>
@@ -37303,22 +37303,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L36" t="n">
-        <v>215</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>169.9067907798016</v>
       </c>
       <c r="P36" t="n">
-        <v>9.59381962508408</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q36" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37458,16 +37458,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>5.216788660003122</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L38" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N38" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O38" t="n">
         <v>150.7019698410586</v>
@@ -37540,16 +37540,16 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L39" t="n">
-        <v>215</v>
+        <v>161.1784674257276</v>
       </c>
       <c r="M39" t="n">
-        <v>110.2009720493049</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O39" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P39" t="n">
         <v>184.4883612256069</v>
@@ -37695,13 +37695,13 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>0.5532456285028686</v>
       </c>
       <c r="L41" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>212.2975967408112</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
         <v>207.9338608153932</v>
@@ -37777,19 +37777,19 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N42" t="n">
-        <v>213</v>
+        <v>107.1131654004615</v>
       </c>
       <c r="O42" t="n">
-        <v>77.7701413557198</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
